--- a/important_mails_2026-04-21.xlsx
+++ b/important_mails_2026-04-21.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,675 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
+          <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Balance paid on your Amazon seller account</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 04/21/26 14:27 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 373,27.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的销售伙伴，
+您好！
+诚邀您参与本次卖家合规策略调研。
+ [点击下方链接，即刻参与调研] (注：问卷精简，均为选择题，只需花费1-2 分钟即可完成)
+问卷链接：https://suv.ma.globalsellingcommunity.cn/t/5RRV0r
+________________________________________
+为什么要参与本次调研？ 在全球电商合规要求持续升级的背景下，您的每一声反馈，都对我们至关重要。
+我们希望更真实地了解卖家当前在合规认知、业务现状以及未来布局规划方面的实际情况。无论是您面临的切身业务挑战，还是对未来长远合规布局的困惑与考虑，都将帮助平台更深入地切中卖家的真实痛点，并直接驱动我们持续优化后续的官方支持方向。
+这不仅仅是一份问卷，我们更希望它能成为亚马逊更好地理解您、支持您出海无忧的一次全新开始。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Prime Day：立即提报您的促销</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Prime Day（日期待公布）：立即提报您的促销
+尊敬的卖家，
+为 2026 年 Prime Day 做好准备 - 为数百万 Prime 会员打造不容错过的优惠！加入我们今年六月的四天活动，通过提报秒杀和Z划算来提升曝光率，从而拓展您的业务！
+如果您在 2026 年 4 月 30 日前提报秒杀或 Z 划算，您将获得每笔固定预付费 30% 的折扣。
+关键日期
+活动日期： 2026年6月 (具体日期待公布)
+提报截止日期： 2026年6月19日
+建议 FBA入仓截止日期：
+欧盟 – 2026年5月27日，英国 – 2026年6月5日
+提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D408225913-Wk17/7z2wg2q/6615577593/h/XJ14pTxdLNF8HtWMzSq-aEmiFGdO6nznpoye9oAUR6I
+您的促销推荐
+以下是您 Prime Day 的ASIN推荐提报列表。 请在卖家中心促销仪表盘查看您的完整推荐列表，每周更新一次，为您提供新机会。
+&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px soli</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>提交商品安全文件以重新启售商品</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96
+ 提交商品安全文件以重新启售商品
+ 尊敬的 Weihai EU：
+您好！
+ 您的部分商品因缺少必要的商品合规信息而被停售。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
+ 为什么会发生这种情况？
+ 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。为了确定此问题，我们综合运用了自动化技术和专家人工评审，最终做出这一决定。
+ 此电子邮件末尾的表格提供了特定于商品的合规性要求。
+ 如何重新启售商品？
+ 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
+-
+ 如果您有所需的文件，请按照相关说明提交您的合规文件。我们仅会重新启售满足合规要求的商品。
+-
+ 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
+ 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
+ 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
+ 如果我未执行上述操作，会怎么样？
+ 如果您未提供所需的合规信息，则受影响的 ASIN 将一直处于停售状态，直到您或其他发布此商品的销售伙伴满足合规要求。
+ 这些商品的亚马逊物流库存会怎样？
+ 您必须在收到本通知后的 30 天内从我们的运营中心移除这些商品。如果未移除，我们将按照《亚马逊服务商业解决方案协议》中的规定弃置此库存，并且费用由您承担。要了解如何移除库存，请参阅 移除库存 帮助页面。
+ 我们愿意随时为您提供帮助。
+ 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
+ 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
+ 亚马逊商品安全与合规性
+ 受影响的商品
+ 详情
+ Roaxkois Töpferset für Kinder, Töpferscheibe, Töpferset für Zuhause mit ton lufttrocknend, Diamant Aufkleber, Kreativ Set für Kinder, Geschenk-Ideen, Geschenk für Mädchen Jungen
+ ASIN： B0F145H325
+ 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
+要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
+儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
+亚马逊根据以下标准来确定商品是否为“儿童玩具”：
+商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
+产品的包装、展示、促销或广告显示该产品适合 14 岁或以下儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Presenta la documentación sobre seguridad del producto para reactivar los listings
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -530,39 +1184,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -578,39 +1232,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -630,39 +1284,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -679,39 +1333,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -729,40 +1383,40 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -779,40 +1433,40 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -829,39 +1483,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -895,39 +1549,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -942,39 +1596,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -990,39 +1644,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -1046,39 +1700,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1097,183 +1751,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
-Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 10/05/2026), we shall dispose of it in accordance with our FBA policies.
-For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
-Thank you for your prompt attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0GKPTF1T7
- SPC-EUAmazon-510175039347142</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Seller Assistant now available in the UK</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Seller Assistant now available in the UK
-[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
-Dear Seller,
-Managing your business on Amazon just got easier.
-[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) is now available in the UK within Seller Central. This AI-powered assistant helps you find relevant information, access insights, and manage your business more efficiently, directly where you already work.
-[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) provides guidance on our tools, policies, and processes using information available across Seller Central, along with personalized responses based on your account data. This allows you to quickly surface insights related to your business performance, inventory planning, listing, compliance, and account health without navigating multiple pages.
-[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-l</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-You recently received a notice about the removal of your listing(s) for the product(s) listed below.
-You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing within 30 days of the notification sent on 03/13/2026. Since a removal order was not submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with FBA policies.
-For more information regarding the restriction of this product, see the notification e-mail you received from Product Safety. If you have additional questions, please contact Seller Support.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
-SPC-USAmazon-862019321040611</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1294,39 +1804,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1341,39 +1851,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -1390,39 +1900,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1436,39 +1946,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1487,40 +1997,40 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1534,39 +2044,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1588,39 +2098,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1643,39 +2153,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1696,39 +2206,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1751,39 +2261,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -1792,39 +2302,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1840,39 +2350,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1892,39 +2402,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1950,39 +2460,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2003,39 +2513,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2061,39 +2571,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2113,40 +2623,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2162,39 +2672,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2214,39 +2724,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2272,39 +2782,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2320,39 +2830,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -2364,39 +2874,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2419,39 +2929,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2475,39 +2985,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -2522,39 +3032,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2568,40 +3078,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2618,39 +3128,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2670,39 +3180,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2719,39 +3229,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2774,39 +3284,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2826,39 +3336,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2875,39 +3385,183 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
+Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 10/05/2026), we shall dispose of it in accordance with our FBA policies.
+For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
+Thank you for your prompt attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0GKPTF1T7
+ SPC-EUAmazon-510175039347142</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Seller Assistant now available in the UK</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Seller Assistant now available in the UK
+[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
+Dear Seller,
+Managing your business on Amazon just got easier.
+[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) is now available in the UK within Seller Central. This AI-powered assistant helps you find relevant information, access insights, and manage your business more efficiently, directly where you already work.
+[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) provides guidance on our tools, policies, and processes using information available across Seller Central, along with personalized responses based on your account data. This allows you to quickly surface insights related to your business performance, inventory planning, listing, compliance, and account health without navigating multiple pages.
+[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-l</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+You recently received a notice about the removal of your listing(s) for the product(s) listed below.
+You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing within 30 days of the notification sent on 03/13/2026. Since a removal order was not submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with FBA policies.
+For more information regarding the restriction of this product, see the notification e-mail you received from Product Safety. If you have additional questions, please contact Seller Support.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
+SPC-USAmazon-862019321040611</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2925,40 +3579,40 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -2976,39 +3630,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -3028,39 +3682,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -3081,39 +3735,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -3134,40 +3788,40 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -3183,39 +3837,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -3238,39 +3892,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3288,39 +3942,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3338,39 +3992,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3390,39 +4044,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3440,39 +4094,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3490,39 +4144,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3540,39 +4194,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3587,39 +4241,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3637,39 +4291,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3687,39 +4341,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3737,39 +4391,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3784,39 +4438,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3831,39 +4485,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3878,39 +4532,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3929,40 +4583,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3981,39 +4635,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4023,39 +4677,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4073,40 +4727,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -4124,39 +4778,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -4189,39 +4843,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -4236,39 +4890,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4287,39 +4941,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -4338,39 +4992,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -4382,39 +5036,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -4430,39 +5084,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -4474,39 +5128,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4521,39 +5175,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4565,39 +5219,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4609,39 +5263,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4653,39 +5307,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4697,39 +5351,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4741,39 +5395,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4785,39 +5439,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4829,39 +5483,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4873,39 +5527,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4917,39 +5571,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4968,39 +5622,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5012,39 +5666,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5056,39 +5710,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5100,39 +5754,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5144,39 +5798,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5188,39 +5842,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5232,39 +5886,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5276,39 +5930,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5327,39 +5981,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5371,40 +6025,40 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5423,39 +6077,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5467,39 +6121,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5518,39 +6172,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -5582,39 +6236,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -5641,39 +6295,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -5685,39 +6339,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -5727,39 +6381,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -5769,39 +6423,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5831,39 +6485,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5881,39 +6535,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5930,39 +6584,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5978,39 +6632,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -6039,39 +6693,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -6092,39 +6746,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6139,39 +6793,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6185,40 +6839,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6234,39 +6888,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6282,39 +6936,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6330,39 +6984,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6378,40 +7032,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6427,39 +7081,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6477,39 +7131,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -6525,39 +7179,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6572,39 +7226,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6619,39 +7273,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6672,40 +7326,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -6720,39 +7374,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -6773,39 +7427,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6818,39 +7472,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6871,39 +7525,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6926,39 +7580,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -6974,39 +7628,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7026,39 +7680,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7077,39 +7731,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7118,39 +7772,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7168,39 +7822,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7230,39 +7884,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7278,39 +7932,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.

--- a/important_mails_2026-04-21.xlsx
+++ b/important_mails_2026-04-21.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1949,7 +1949,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1964,119 +1964,21 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
+          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 12354633592] 其他账户问题</t>
+          <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的销售伙伴：
-您好！
-我叫 John Raghul Singh S,来自亚马逊 销售 合作伙伴,今天我将帮助您调查 ASINs: B0G6XCTGJC, B0G6ZCHV7Z 和 B0GKPTF1T7 存在缺陷的不可售库存问题的请求。
-关于ASINs: B0G6XCTGJC, B0G6ZCHV7Z。
-我们已检查并确认ASINs的商品已从缺陷状态移至可售状态。
-您可以通过以下链接确认这一点:
-https://sellercentral-europe.amazon.com/myinventory/inventory?fulfilledBy=all&amp;page=1&amp;pageSize=250&amp;searchField=all&amp;searchTerm=B0G6XCTGJC&amp;sort=sales_desc&amp;status=all&amp;ref_=xx_invmgr_favb_xx
-https://sellercentral-europe.amazon.com/myinventory/inventory?fulfilledBy=all&amp;page=1&amp;pageSize=250&amp;searchField=all&amp;searchTerm=X002C14QJT&amp;sort=sales_desc&amp;status=all&amp;ref_=xx_invmgr_favb_xx
-https://sellercentral-europe.amazon.com/reportcentral/LEDGER_REPORT/0/%7B%22filters%22:[%22%22,%22B0G6XCTGJC%22,%22DAILY%22,%22FC%22,%2284700%22,%22%22,%22Adjustments%22,%22Damaged%22,%22Destroyed%22,%22Found%22,%22Lost%22,%22Other%22,%22%22,%22pageOffset%22:1,%22searchDays%22:30 %7D
-https://sellercentral-europe.amazon.com/reportcentral/LEDGER_REPORT/0/%7B%22filters%22:[%22%22,%22B0G6ZCHV7Z%22,%22DAILY%22,%22FC%22,%2284700%22,%22%22,%22Adjustments%22,%22Damaged%22,%22Destroyed%22,%22Found%22,%22Lost%22,%22Other%22,%22%22,%22pageOffset%22:1,%22searchDays%22:30 %7D
-关于ASIN: B0GKPTF1T7
-我们的团队仍在为您调查此问题。
-收到更新信息后,我们会向您更新详细信息。
-请您耐</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
- Product Support</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
- Enrol now into Amazon Product Support !
- Hello,
- Greetings from Amazon Product Support.
- Every product returned costs time, money and customer trust. That’s why Amazon offers product support – a suite of post-purchase solutions that help customers solve problems quickly and keep products in use. In 2025, approximately 50% of customers who engaged with Product Support did not return their product. *
- Enrol now and learn more about Amazon Product Support
- Here’s how you can reduce returns and help customers:
- • Manufacturer support – A customer has a question about your product? They can contact your experts directly. In 2025, approximately 64% of customers who contacted support through Manufacturer support did not return their product. * Available in the US, Canada, UK, Germany, France, Italy, Spain, Belgium, Sweden, Poland and the Netherlands.
- • Brand integration – call &amp; chat – A customer runs into a setup issue and wants instant help? Provide live calls or chat support. In 2025, approximately 58% of customers who contacted support through Brand integration – call &amp; chat did not return the product. * Available in the US, Canada, UK, Germany, France, Italy, Spain, Belgium, Swe</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-30</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2098,39 +2000,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2153,147 +2055,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-23</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-23 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRCC2H56 Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- G0pQwXa92J
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -2302,39 +2096,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -2350,39 +2144,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2402,39 +2196,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2460,39 +2254,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2513,39 +2307,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2571,39 +2365,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2623,40 +2417,40 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2672,39 +2466,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2724,39 +2518,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2782,39 +2576,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2830,39 +2624,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -2874,39 +2668,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2929,39 +2723,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2985,39 +2779,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3032,39 +2826,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3078,40 +2872,40 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3128,39 +2922,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3180,39 +2974,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3229,39 +3023,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3284,39 +3078,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3336,39 +3130,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3385,39 +3179,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -3433,39 +3227,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -3477,39 +3271,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3529,39 +3323,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3579,40 +3373,40 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3630,39 +3424,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -3682,39 +3476,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -3735,39 +3529,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -3788,40 +3582,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -3837,39 +3631,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -3892,39 +3686,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3942,39 +3736,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3992,39 +3786,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -4044,39 +3838,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4094,39 +3888,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4144,39 +3938,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4194,39 +3988,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -4241,39 +4035,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4291,39 +4085,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4341,39 +4135,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4391,39 +4185,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4438,39 +4232,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4485,39 +4279,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4532,39 +4326,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4583,40 +4377,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -4635,39 +4429,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4677,90 +4471,138 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12354633592] 其他账户问题</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的销售伙伴：
+您好！
+我叫 John Raghul Singh S,来自亚马逊 销售 合作伙伴,今天我将帮助您调查 ASINs: B0G6XCTGJC, B0G6ZCHV7Z 和 B0GKPTF1T7 存在缺陷的不可售库存问题的请求。
+关于ASINs: B0G6XCTGJC, B0G6ZCHV7Z。
+我们已检查并确认ASINs的商品已从缺陷状态移至可售状态。
+您可以通过以下链接确认这一点:
+https://sellercentral-europe.amazon.com/myinventory/inventory?fulfilledBy=all&amp;page=1&amp;pageSize=250&amp;searchField=all&amp;searchTerm=B0G6XCTGJC&amp;sort=sales_desc&amp;status=all&amp;ref_=xx_invmgr_favb_xx
+https://sellercentral-europe.amazon.com/myinventory/inventory?fulfilledBy=all&amp;page=1&amp;pageSize=250&amp;searchField=all&amp;searchTerm=X002C14QJT&amp;sort=sales_desc&amp;status=all&amp;ref_=xx_invmgr_favb_xx
+https://sellercentral-europe.amazon.com/reportcentral/LEDGER_REPORT/0/%7B%22filters%22:[%22%22,%22B0G6XCTGJC%22,%22DAILY%22,%22FC%22,%2284700%22,%22%22,%22Adjustments%22,%22Damaged%22,%22Destroyed%22,%22Found%22,%22Lost%22,%22Other%22,%22%22,%22pageOffset%22:1,%22searchDays%22:30 %7D
+https://sellercentral-europe.amazon.com/reportcentral/LEDGER_REPORT/0/%7B%22filters%22:[%22%22,%22B0G6ZCHV7Z%22,%22DAILY%22,%22FC%22,%2284700%22,%22%22,%22Adjustments%22,%22Damaged%22,%22Destroyed%22,%22Found%22,%22Lost%22,%22Other%22,%22%22,%22pageOffset%22:1,%22searchDays%22:30 %7D
+关于ASIN: B0GKPTF1T7
+我们的团队仍在为您调查此问题。
+收到更新信息后,我们会向您更新详细信息。
+请您耐</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
+ Product Support</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Enrol now into Amazon Product Support !
+ Hello,
+ Greetings from Amazon Product Support.
+ Every product returned costs time, money and customer trust. That’s why Amazon offers product support – a suite of post-purchase solutions that help customers solve problems quickly and keep products in use. In 2025, approximately 50% of customers who engaged with Product Support did not return their product. *
+ Enrol now and learn more about Amazon Product Support
+ Here’s how you can reduce returns and help customers:
+ • Manufacturer support – A customer has a question about your product? They can contact your experts directly. In 2025, approximately 64% of customers who contacted support through Manufacturer support did not return their product. * Available in the US, Canada, UK, Germany, France, Italy, Spain, Belgium, Sweden, Poland and the Netherlands.
+ • Brand integration – call &amp; chat – A customer runs into a setup issue and wants instant help? Provide live calls or chat support. In 2025, approximately 58% of customers who contacted support through Brand integration – call &amp; chat did not return the product. * Available in the US, Canada, UK, Germany, France, Italy, Spain, Belgium, Swe</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -4778,39 +4620,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -4843,39 +4685,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -4890,39 +4732,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4941,39 +4783,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -4992,39 +4834,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -5036,39 +4878,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -5084,39 +4926,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -5128,39 +4970,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5175,39 +5017,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5219,39 +5061,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5263,39 +5105,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5307,39 +5149,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5351,39 +5193,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5395,39 +5237,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5439,39 +5281,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5483,39 +5325,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5527,39 +5369,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5571,39 +5413,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5622,39 +5464,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5666,39 +5508,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5710,39 +5552,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5754,39 +5596,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5798,39 +5640,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5842,39 +5684,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5886,39 +5728,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5930,39 +5772,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5981,39 +5823,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6025,40 +5867,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6077,39 +5919,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6121,39 +5963,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6172,39 +6014,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -6236,39 +6078,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -6295,39 +6137,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -6339,39 +6181,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -6381,39 +6223,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -6423,39 +6265,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -6485,39 +6327,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6535,39 +6377,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6584,39 +6426,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6632,39 +6474,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -6693,39 +6535,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -6746,39 +6588,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6793,39 +6635,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6839,40 +6681,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6888,39 +6730,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6936,39 +6778,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6984,39 +6826,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7032,40 +6874,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7081,39 +6923,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7131,39 +6973,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -7179,39 +7021,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7226,39 +7068,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -7273,39 +7115,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7326,40 +7168,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -7374,39 +7216,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -7427,39 +7269,147 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-04-23</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-23 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRCC2H56 Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- G0pQwXa92J
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -7472,39 +7422,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7525,39 +7475,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7580,39 +7530,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -7628,39 +7578,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7680,39 +7630,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7731,39 +7681,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7772,39 +7722,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7822,39 +7772,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7884,39 +7834,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7932,54 +7882,6 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] – Update Inventory -FBA</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
-We recommend that you inbound additional inventory for your products immediately. To view the recommended replenishment quantity for these ASINs, go to “Restock inventory”:
-https://sellercentral.amazon.ca/restockinventory/recommendations
-Here is a sample of your high selling FBA ASINs, which are considered low in stock at the moment:
-B0DMFL5X12
-You can download the full list of your ASIN at risk of out of stock at the following link:  https://www.sellercentral.amazon.ca/reportcentral/RestockReport/1
-For more information about Restock tool, you can visit this help page - https://sellercentral.amazon.ca/gp/help/G201634550
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this report to the correct point of contact.
-If you wish to unsubscribe please REPLY ALL with the subject line ‘Unsubsc</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
